--- a/Team-Data/2013-14/1-2-2013-14.xlsx
+++ b/Team-Data/2013-14/1-2-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>1.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
@@ -757,10 +824,10 @@
         <v>9</v>
       </c>
       <c r="AJ2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL2" t="n">
         <v>4</v>
@@ -772,22 +839,22 @@
         <v>7</v>
       </c>
       <c r="AO2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP2" t="n">
         <v>20</v>
       </c>
-      <c r="AP2" t="n">
-        <v>19</v>
-      </c>
       <c r="AQ2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR2" t="n">
         <v>29</v>
       </c>
       <c r="AS2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AT2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU2" t="n">
         <v>1</v>
@@ -799,7 +866,7 @@
         <v>11</v>
       </c>
       <c r="AX2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
@@ -808,10 +875,10 @@
         <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BC2" t="n">
         <v>12</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-2-2013-14</t>
+          <t>2014-01-02</t>
         </is>
       </c>
     </row>
@@ -843,37 +910,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E3" t="n">
         <v>13</v>
       </c>
       <c r="F3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G3" t="n">
-        <v>0.406</v>
+        <v>0.419</v>
       </c>
       <c r="H3" t="n">
         <v>48</v>
       </c>
       <c r="I3" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="J3" t="n">
         <v>80.90000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L3" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="N3" t="n">
-        <v>0.346</v>
+        <v>0.35</v>
       </c>
       <c r="O3" t="n">
         <v>15.5</v>
@@ -882,55 +949,55 @@
         <v>20.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.763</v>
+        <v>0.766</v>
       </c>
       <c r="R3" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="S3" t="n">
-        <v>31.7</v>
+        <v>31.5</v>
       </c>
       <c r="T3" t="n">
-        <v>41.8</v>
+        <v>41.6</v>
       </c>
       <c r="U3" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="V3" t="n">
-        <v>16.2</v>
+        <v>16</v>
       </c>
       <c r="W3" t="n">
         <v>6.8</v>
       </c>
       <c r="X3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Y3" t="n">
         <v>4.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="AA3" t="n">
         <v>18.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>94.7</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>-2</v>
+        <v>-1.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AE3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG3" t="n">
         <v>20</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>21</v>
       </c>
       <c r="AH3" t="n">
         <v>27</v>
@@ -942,7 +1009,7 @@
         <v>25</v>
       </c>
       <c r="AK3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AL3" t="n">
         <v>25</v>
@@ -951,49 +1018,49 @@
         <v>25</v>
       </c>
       <c r="AN3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AO3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AR3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS3" t="n">
         <v>18</v>
       </c>
       <c r="AT3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AU3" t="n">
         <v>30</v>
       </c>
       <c r="AV3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW3" t="n">
         <v>26</v>
       </c>
       <c r="AX3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY3" t="n">
         <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BC3" t="n">
         <v>18</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-2-2013-14</t>
+          <t>2014-01-02</t>
         </is>
       </c>
     </row>
@@ -1025,25 +1092,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
         <v>21</v>
       </c>
       <c r="G4" t="n">
-        <v>0.344</v>
+        <v>0.323</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>34.8</v>
+        <v>34.9</v>
       </c>
       <c r="J4" t="n">
-        <v>78.2</v>
+        <v>78.5</v>
       </c>
       <c r="K4" t="n">
         <v>0.444</v>
@@ -1052,16 +1119,16 @@
         <v>7.4</v>
       </c>
       <c r="M4" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="N4" t="n">
         <v>0.372</v>
       </c>
       <c r="O4" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="P4" t="n">
-        <v>26.1</v>
+        <v>25.9</v>
       </c>
       <c r="Q4" t="n">
         <v>0.759</v>
@@ -1070,52 +1137,52 @@
         <v>9.6</v>
       </c>
       <c r="S4" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="T4" t="n">
-        <v>39.8</v>
+        <v>40</v>
       </c>
       <c r="U4" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V4" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W4" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="X4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y4" t="n">
         <v>3.9</v>
       </c>
-      <c r="Y4" t="n">
-        <v>4</v>
-      </c>
       <c r="Z4" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AB4" t="n">
         <v>96.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>-5.4</v>
+        <v>-5.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
         <v>23</v>
       </c>
       <c r="AF4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI4" t="n">
         <v>28</v>
@@ -1133,22 +1200,22 @@
         <v>21</v>
       </c>
       <c r="AN4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP4" t="n">
         <v>4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR4" t="n">
         <v>25</v>
       </c>
       <c r="AS4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT4" t="n">
         <v>28</v>
@@ -1157,25 +1224,25 @@
         <v>21</v>
       </c>
       <c r="AV4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW4" t="n">
         <v>25</v>
       </c>
       <c r="AX4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BA4" t="n">
         <v>7</v>
       </c>
       <c r="BB4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC4" t="n">
         <v>26</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-2-2013-14</t>
+          <t>2014-01-02</t>
         </is>
       </c>
     </row>
@@ -1207,25 +1274,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E5" t="n">
         <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G5" t="n">
-        <v>0.412</v>
+        <v>0.424</v>
       </c>
       <c r="H5" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I5" t="n">
         <v>34.5</v>
       </c>
       <c r="J5" t="n">
-        <v>82.2</v>
+        <v>82.3</v>
       </c>
       <c r="K5" t="n">
         <v>0.42</v>
@@ -1237,67 +1304,67 @@
         <v>15.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.327</v>
+        <v>0.324</v>
       </c>
       <c r="O5" t="n">
-        <v>18.5</v>
+        <v>18.2</v>
       </c>
       <c r="P5" t="n">
-        <v>25.4</v>
+        <v>25.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.729</v>
+        <v>0.726</v>
       </c>
       <c r="R5" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S5" t="n">
-        <v>32.6</v>
+        <v>32.9</v>
       </c>
       <c r="T5" t="n">
-        <v>43.1</v>
+        <v>43.5</v>
       </c>
       <c r="U5" t="n">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="V5" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="W5" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="X5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>92.59999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.9</v>
+        <v>-2.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE5" t="n">
         <v>14</v>
       </c>
       <c r="AF5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AH5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI5" t="n">
         <v>29</v>
@@ -1315,25 +1382,25 @@
         <v>29</v>
       </c>
       <c r="AN5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AP5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT5" t="n">
         <v>13</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>15</v>
       </c>
       <c r="AU5" t="n">
         <v>26</v>
@@ -1345,7 +1412,7 @@
         <v>29</v>
       </c>
       <c r="AX5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY5" t="n">
         <v>22</v>
@@ -1357,10 +1424,10 @@
         <v>9</v>
       </c>
       <c r="BB5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-2-2013-14</t>
+          <t>2014-01-02</t>
         </is>
       </c>
     </row>
@@ -1389,67 +1456,67 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F6" t="n">
         <v>18</v>
       </c>
       <c r="G6" t="n">
-        <v>0.419</v>
+        <v>0.4</v>
       </c>
       <c r="H6" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I6" t="n">
         <v>33.9</v>
       </c>
       <c r="J6" t="n">
-        <v>80.3</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.422</v>
+        <v>0.423</v>
       </c>
       <c r="L6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="M6" t="n">
         <v>16.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.321</v>
+        <v>0.327</v>
       </c>
       <c r="O6" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="P6" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.776</v>
+        <v>0.775</v>
       </c>
       <c r="R6" t="n">
         <v>11.8</v>
       </c>
       <c r="S6" t="n">
-        <v>32.6</v>
+        <v>32.8</v>
       </c>
       <c r="T6" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
       <c r="U6" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="V6" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="W6" t="n">
         <v>6.7</v>
       </c>
       <c r="X6" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y6" t="n">
         <v>6.6</v>
@@ -1458,28 +1525,28 @@
         <v>19.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>91.40000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>-1.1</v>
+        <v>-1.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AF6" t="n">
         <v>18</v>
       </c>
       <c r="AG6" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AH6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI6" t="n">
         <v>30</v>
@@ -1497,22 +1564,22 @@
         <v>28</v>
       </c>
       <c r="AN6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT6" t="n">
         <v>8</v>
@@ -1542,7 +1609,7 @@
         <v>30</v>
       </c>
       <c r="BC6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-2-2013-14</t>
+          <t>2014-01-02</t>
         </is>
       </c>
     </row>
@@ -1571,37 +1638,37 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
         <v>21</v>
       </c>
       <c r="G7" t="n">
-        <v>0.344</v>
+        <v>0.323</v>
       </c>
       <c r="H7" t="n">
-        <v>49.3</v>
+        <v>49.1</v>
       </c>
       <c r="I7" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="J7" t="n">
-        <v>86</v>
+        <v>85.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0.424</v>
+        <v>0.426</v>
       </c>
       <c r="L7" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M7" t="n">
         <v>19.7</v>
       </c>
       <c r="N7" t="n">
-        <v>0.353</v>
+        <v>0.357</v>
       </c>
       <c r="O7" t="n">
         <v>16.1</v>
@@ -1610,31 +1677,31 @@
         <v>21.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.752</v>
+        <v>0.754</v>
       </c>
       <c r="R7" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="S7" t="n">
-        <v>32.2</v>
+        <v>31.9</v>
       </c>
       <c r="T7" t="n">
-        <v>44.1</v>
+        <v>43.6</v>
       </c>
       <c r="U7" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="V7" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W7" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="Z7" t="n">
         <v>19.3</v>
@@ -1643,31 +1710,31 @@
         <v>19.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>95.90000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>-5.8</v>
+        <v>-6.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
         <v>23</v>
       </c>
       <c r="AF7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH7" t="n">
         <v>1</v>
       </c>
       <c r="AI7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK7" t="n">
         <v>27</v>
@@ -1679,7 +1746,7 @@
         <v>23</v>
       </c>
       <c r="AN7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO7" t="n">
         <v>21</v>
@@ -1691,28 +1758,28 @@
         <v>18</v>
       </c>
       <c r="AR7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AT7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AU7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY7" t="n">
         <v>27</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>28</v>
       </c>
       <c r="AZ7" t="n">
         <v>6</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-2-2013-14</t>
+          <t>2014-01-02</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1849,13 +1916,13 @@
         <v>5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK8" t="n">
         <v>5</v>
       </c>
       <c r="AL8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM8" t="n">
         <v>11</v>
@@ -1864,7 +1931,7 @@
         <v>8</v>
       </c>
       <c r="AO8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP8" t="n">
         <v>27</v>
@@ -1885,13 +1952,13 @@
         <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
       </c>
       <c r="AX8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY8" t="n">
         <v>4</v>
@@ -1900,10 +1967,10 @@
         <v>11</v>
       </c>
       <c r="BA8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BC8" t="n">
         <v>11</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-2-2013-14</t>
+          <t>2014-01-02</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-1.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AE9" t="n">
         <v>14</v>
@@ -2043,16 +2110,16 @@
         <v>15</v>
       </c>
       <c r="AN9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AO9" t="n">
         <v>8</v>
       </c>
       <c r="AP9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AR9" t="n">
         <v>5</v>
@@ -2061,7 +2128,7 @@
         <v>9</v>
       </c>
       <c r="AT9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU9" t="n">
         <v>16</v>
@@ -2076,7 +2143,7 @@
         <v>6</v>
       </c>
       <c r="AY9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ9" t="n">
         <v>22</v>
@@ -2088,7 +2155,7 @@
         <v>16</v>
       </c>
       <c r="BC9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-2-2013-14</t>
+          <t>2014-01-02</t>
         </is>
       </c>
     </row>
@@ -2195,25 +2262,25 @@
         <v>-2.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE10" t="n">
         <v>14</v>
       </c>
       <c r="AF10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG10" t="n">
         <v>18</v>
       </c>
       <c r="AH10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI10" t="n">
         <v>10</v>
       </c>
       <c r="AJ10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK10" t="n">
         <v>14</v>
@@ -2228,7 +2295,7 @@
         <v>30</v>
       </c>
       <c r="AO10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP10" t="n">
         <v>10</v>
@@ -2240,7 +2307,7 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT10" t="n">
         <v>9</v>
@@ -2255,16 +2322,16 @@
         <v>4</v>
       </c>
       <c r="AX10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY10" t="n">
         <v>13</v>
       </c>
       <c r="AZ10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB10" t="n">
         <v>15</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-2-2013-14</t>
+          <t>2014-01-02</t>
         </is>
       </c>
     </row>
@@ -2299,37 +2366,37 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F11" t="n">
         <v>13</v>
       </c>
       <c r="G11" t="n">
-        <v>0.618</v>
+        <v>0.606</v>
       </c>
       <c r="H11" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I11" t="n">
-        <v>39.1</v>
+        <v>38.9</v>
       </c>
       <c r="J11" t="n">
         <v>84.2</v>
       </c>
       <c r="K11" t="n">
-        <v>0.464</v>
+        <v>0.462</v>
       </c>
       <c r="L11" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="M11" t="n">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="N11" t="n">
-        <v>0.397</v>
+        <v>0.393</v>
       </c>
       <c r="O11" t="n">
         <v>15.7</v>
@@ -2338,31 +2405,31 @@
         <v>21.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.729</v>
+        <v>0.725</v>
       </c>
       <c r="R11" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S11" t="n">
         <v>35.4</v>
       </c>
       <c r="T11" t="n">
-        <v>46.4</v>
+        <v>46.6</v>
       </c>
       <c r="U11" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="V11" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="W11" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X11" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z11" t="n">
         <v>22.6</v>
@@ -2371,34 +2438,34 @@
         <v>19.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>103.4</v>
+        <v>102.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF11" t="n">
         <v>8</v>
       </c>
       <c r="AG11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AH11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AL11" t="n">
         <v>3</v>
@@ -2410,16 +2477,16 @@
         <v>3</v>
       </c>
       <c r="AO11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AP11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AS11" t="n">
         <v>2</v>
@@ -2428,7 +2495,7 @@
         <v>2</v>
       </c>
       <c r="AU11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV11" t="n">
         <v>29</v>
@@ -2437,7 +2504,7 @@
         <v>16</v>
       </c>
       <c r="AX11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY11" t="n">
         <v>15</v>
@@ -2449,7 +2516,7 @@
         <v>19</v>
       </c>
       <c r="BB11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="BC11" t="n">
         <v>7</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-2-2013-14</t>
+          <t>2014-01-02</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>3.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE12" t="n">
         <v>7</v>
@@ -2568,10 +2635,10 @@
         <v>8</v>
       </c>
       <c r="AG12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AI12" t="n">
         <v>15</v>
@@ -2589,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO12" t="n">
         <v>2</v>
@@ -2616,7 +2683,7 @@
         <v>28</v>
       </c>
       <c r="AW12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX12" t="n">
         <v>3</v>
@@ -2625,16 +2692,16 @@
         <v>20</v>
       </c>
       <c r="AZ12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
       </c>
       <c r="BB12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-2-2013-14</t>
+          <t>2014-01-02</t>
         </is>
       </c>
     </row>
@@ -2741,10 +2808,10 @@
         <v>8.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF13" t="n">
         <v>1</v>
@@ -2753,7 +2820,7 @@
         <v>1</v>
       </c>
       <c r="AH13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI13" t="n">
         <v>23</v>
@@ -2762,7 +2829,7 @@
         <v>27</v>
       </c>
       <c r="AK13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL13" t="n">
         <v>18</v>
@@ -2777,19 +2844,19 @@
         <v>10</v>
       </c>
       <c r="AP13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ13" t="n">
         <v>5</v>
       </c>
       <c r="AR13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS13" t="n">
         <v>3</v>
       </c>
       <c r="AT13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU13" t="n">
         <v>17</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-2-2013-14</t>
+          <t>2014-01-02</t>
         </is>
       </c>
     </row>
@@ -2923,28 +2990,28 @@
         <v>5.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
         <v>6</v>
       </c>
       <c r="AF14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG14" t="n">
         <v>6</v>
       </c>
       <c r="AH14" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AI14" t="n">
         <v>13</v>
       </c>
       <c r="AJ14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL14" t="n">
         <v>12</v>
@@ -2968,10 +3035,10 @@
         <v>21</v>
       </c>
       <c r="AS14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU14" t="n">
         <v>5</v>
@@ -2983,7 +3050,7 @@
         <v>10</v>
       </c>
       <c r="AX14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY14" t="n">
         <v>2</v>
@@ -2995,7 +3062,7 @@
         <v>2</v>
       </c>
       <c r="BB14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC14" t="n">
         <v>6</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-2-2013-14</t>
+          <t>2014-01-02</t>
         </is>
       </c>
     </row>
@@ -3105,13 +3172,13 @@
         <v>-4.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF15" t="n">
         <v>20</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>19</v>
       </c>
       <c r="AG15" t="n">
         <v>21</v>
@@ -3120,7 +3187,7 @@
         <v>27</v>
       </c>
       <c r="AI15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ15" t="n">
         <v>12</v>
@@ -3141,19 +3208,19 @@
         <v>16</v>
       </c>
       <c r="AP15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR15" t="n">
         <v>22</v>
       </c>
       <c r="AS15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU15" t="n">
         <v>13</v>
@@ -3168,19 +3235,19 @@
         <v>4</v>
       </c>
       <c r="AY15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB15" t="n">
         <v>18</v>
       </c>
       <c r="BC15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-2-2013-14</t>
+          <t>2014-01-02</t>
         </is>
       </c>
     </row>
@@ -3209,61 +3276,61 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F16" t="n">
         <v>17</v>
       </c>
       <c r="G16" t="n">
-        <v>0.452</v>
+        <v>0.433</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>37.2</v>
+        <v>37</v>
       </c>
       <c r="J16" t="n">
-        <v>82.59999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="K16" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="M16" t="n">
         <v>14.1</v>
       </c>
       <c r="N16" t="n">
-        <v>0.341</v>
+        <v>0.345</v>
       </c>
       <c r="O16" t="n">
-        <v>15.5</v>
+        <v>15.8</v>
       </c>
       <c r="P16" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.752</v>
+        <v>0.756</v>
       </c>
       <c r="R16" t="n">
-        <v>12.3</v>
+        <v>12</v>
       </c>
       <c r="S16" t="n">
-        <v>30.6</v>
+        <v>30.3</v>
       </c>
       <c r="T16" t="n">
-        <v>42.9</v>
+        <v>42.4</v>
       </c>
       <c r="U16" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="V16" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="W16" t="n">
         <v>7.5</v>
@@ -3275,40 +3342,40 @@
         <v>5.9</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA16" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE16" t="n">
         <v>19</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>14</v>
       </c>
       <c r="AF16" t="n">
         <v>16</v>
       </c>
       <c r="AG16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH16" t="n">
         <v>19</v>
       </c>
       <c r="AI16" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AJ16" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AK16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3317,25 +3384,25 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO16" t="n">
         <v>22</v>
       </c>
-      <c r="AO16" t="n">
-        <v>25</v>
-      </c>
       <c r="AP16" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AQ16" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AR16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS16" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AT16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AU16" t="n">
         <v>15</v>
@@ -3344,7 +3411,7 @@
         <v>4</v>
       </c>
       <c r="AW16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX16" t="n">
         <v>27</v>
@@ -3353,16 +3420,16 @@
         <v>23</v>
       </c>
       <c r="AZ16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BA16" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB16" t="n">
         <v>26</v>
       </c>
-      <c r="BB16" t="n">
-        <v>25</v>
-      </c>
       <c r="BC16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-2-2013-14</t>
+          <t>2014-01-02</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E17" t="n">
         <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G17" t="n">
-        <v>0.75</v>
+        <v>0.774</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3409,40 +3476,40 @@
         <v>39.2</v>
       </c>
       <c r="J17" t="n">
-        <v>76.7</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K17" t="n">
         <v>0.511</v>
       </c>
       <c r="L17" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M17" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="N17" t="n">
-        <v>0.386</v>
+        <v>0.384</v>
       </c>
       <c r="O17" t="n">
-        <v>18</v>
+        <v>17.8</v>
       </c>
       <c r="P17" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.756</v>
+        <v>0.753</v>
       </c>
       <c r="R17" t="n">
         <v>6.5</v>
       </c>
       <c r="S17" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T17" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="U17" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="V17" t="n">
         <v>15.3</v>
@@ -3451,7 +3518,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="X17" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y17" t="n">
         <v>2.8</v>
@@ -3460,22 +3527,22 @@
         <v>19.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>104.8</v>
+        <v>104.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
       </c>
       <c r="AF17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG17" t="n">
         <v>5</v>
@@ -3493,7 +3560,7 @@
         <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AM17" t="n">
         <v>13</v>
@@ -3502,34 +3569,34 @@
         <v>5</v>
       </c>
       <c r="AO17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP17" t="n">
         <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
       </c>
       <c r="AS17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV17" t="n">
         <v>15</v>
       </c>
       <c r="AW17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3538,10 +3605,10 @@
         <v>9</v>
       </c>
       <c r="BA17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC17" t="n">
         <v>4</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-2-2013-14</t>
+          <t>2014-01-02</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E18" t="n">
         <v>7</v>
       </c>
       <c r="F18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G18" t="n">
-        <v>0.219</v>
+        <v>0.226</v>
       </c>
       <c r="H18" t="n">
         <v>49.1</v>
@@ -3591,43 +3658,43 @@
         <v>35</v>
       </c>
       <c r="J18" t="n">
-        <v>82.90000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.422</v>
+        <v>0.421</v>
       </c>
       <c r="L18" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M18" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0.339</v>
+        <v>0.344</v>
       </c>
       <c r="O18" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="P18" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="Q18" t="n">
         <v>0.772</v>
       </c>
       <c r="R18" t="n">
-        <v>11.1</v>
+        <v>11.3</v>
       </c>
       <c r="S18" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="T18" t="n">
-        <v>41.4</v>
+        <v>41.6</v>
       </c>
       <c r="U18" t="n">
         <v>20.6</v>
       </c>
       <c r="V18" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W18" t="n">
         <v>7.2</v>
@@ -3642,34 +3709,34 @@
         <v>20.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>92.5</v>
+        <v>92.7</v>
       </c>
       <c r="AC18" t="n">
         <v>-7.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
       </c>
       <c r="AF18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG18" t="n">
         <v>30</v>
       </c>
       <c r="AH18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI18" t="n">
         <v>27</v>
       </c>
       <c r="AJ18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK18" t="n">
         <v>29</v>
@@ -3681,31 +3748,31 @@
         <v>18</v>
       </c>
       <c r="AN18" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AO18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP18" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AQ18" t="n">
         <v>9</v>
       </c>
       <c r="AR18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AS18" t="n">
         <v>25</v>
       </c>
       <c r="AT18" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AU18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV18" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AW18" t="n">
         <v>23</v>
@@ -3720,10 +3787,10 @@
         <v>17</v>
       </c>
       <c r="BA18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BB18" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BC18" t="n">
         <v>28</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-2-2013-14</t>
+          <t>2014-01-02</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>4.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE19" t="n">
         <v>12</v>
@@ -3845,7 +3912,7 @@
         <v>12</v>
       </c>
       <c r="AH19" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI19" t="n">
         <v>11</v>
@@ -3881,7 +3948,7 @@
         <v>16</v>
       </c>
       <c r="AT19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU19" t="n">
         <v>6</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-2-2013-14</t>
+          <t>2014-01-02</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AE20" t="n">
         <v>14</v>
@@ -4051,7 +4118,7 @@
         <v>15</v>
       </c>
       <c r="AP20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ20" t="n">
         <v>11</v>
@@ -4060,10 +4127,10 @@
         <v>3</v>
       </c>
       <c r="AS20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU20" t="n">
         <v>11</v>
@@ -4072,13 +4139,13 @@
         <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX20" t="n">
         <v>1</v>
       </c>
       <c r="AY20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ20" t="n">
         <v>23</v>
@@ -4087,7 +4154,7 @@
         <v>20</v>
       </c>
       <c r="BB20" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BC20" t="n">
         <v>14</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-2-2013-14</t>
+          <t>2014-01-02</t>
         </is>
       </c>
     </row>
@@ -4119,52 +4186,52 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F21" t="n">
         <v>21</v>
       </c>
       <c r="G21" t="n">
-        <v>0.323</v>
+        <v>0.3</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
       </c>
       <c r="I21" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J21" t="n">
-        <v>83.3</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.432</v>
+        <v>0.43</v>
       </c>
       <c r="L21" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="N21" t="n">
-        <v>0.357</v>
+        <v>0.353</v>
       </c>
       <c r="O21" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="P21" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.767</v>
+        <v>0.763</v>
       </c>
       <c r="R21" t="n">
         <v>10.5</v>
       </c>
       <c r="S21" t="n">
-        <v>28.6</v>
+        <v>28.5</v>
       </c>
       <c r="T21" t="n">
         <v>39.1</v>
@@ -4188,37 +4255,37 @@
         <v>22.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>95</v>
+        <v>94.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>-4.3</v>
+        <v>-4.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE21" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AF21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG21" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AH21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI21" t="n">
         <v>24</v>
       </c>
       <c r="AJ21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL21" t="n">
         <v>7</v>
@@ -4227,7 +4294,7 @@
         <v>6</v>
       </c>
       <c r="AN21" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AO21" t="n">
         <v>30</v>
@@ -4236,10 +4303,10 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AR21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS21" t="n">
         <v>30</v>
@@ -4260,19 +4327,19 @@
         <v>17</v>
       </c>
       <c r="AY21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ21" t="n">
         <v>29</v>
       </c>
       <c r="BA21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-2-2013-14</t>
+          <t>2014-01-02</t>
         </is>
       </c>
     </row>
@@ -4301,28 +4368,28 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E22" t="n">
         <v>25</v>
       </c>
       <c r="F22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G22" t="n">
-        <v>0.781</v>
+        <v>0.806</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
       </c>
       <c r="I22" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="J22" t="n">
-        <v>82.59999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.471</v>
+        <v>0.47</v>
       </c>
       <c r="L22" t="n">
         <v>6.8</v>
@@ -4331,31 +4398,31 @@
         <v>19.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0.352</v>
+        <v>0.35</v>
       </c>
       <c r="O22" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="P22" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="Q22" t="n">
         <v>0.8149999999999999</v>
       </c>
       <c r="R22" t="n">
-        <v>10.7</v>
+        <v>10.9</v>
       </c>
       <c r="S22" t="n">
-        <v>36.4</v>
+        <v>36.7</v>
       </c>
       <c r="T22" t="n">
-        <v>47.1</v>
+        <v>47.5</v>
       </c>
       <c r="U22" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="V22" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="W22" t="n">
         <v>7.8</v>
@@ -4367,37 +4434,37 @@
         <v>4</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AA22" t="n">
         <v>20.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>105.3</v>
+        <v>105.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AE22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH22" t="n">
         <v>20</v>
       </c>
       <c r="AI22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ22" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AK22" t="n">
         <v>4</v>
@@ -4409,13 +4476,13 @@
         <v>24</v>
       </c>
       <c r="AN22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO22" t="n">
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AQ22" t="n">
         <v>2</v>
@@ -4433,7 +4500,7 @@
         <v>12</v>
       </c>
       <c r="AV22" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AW22" t="n">
         <v>14</v>
@@ -4442,16 +4509,16 @@
         <v>2</v>
       </c>
       <c r="AY22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ22" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BA22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-2-2013-14</t>
+          <t>2014-01-02</t>
         </is>
       </c>
     </row>
@@ -4483,67 +4550,67 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E23" t="n">
         <v>10</v>
       </c>
       <c r="F23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G23" t="n">
-        <v>0.313</v>
+        <v>0.323</v>
       </c>
       <c r="H23" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I23" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="J23" t="n">
-        <v>82.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.445</v>
+        <v>0.447</v>
       </c>
       <c r="L23" t="n">
         <v>7.4</v>
       </c>
       <c r="M23" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="N23" t="n">
-        <v>0.352</v>
+        <v>0.354</v>
       </c>
       <c r="O23" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="P23" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.748</v>
+        <v>0.753</v>
       </c>
       <c r="R23" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="S23" t="n">
-        <v>33.4</v>
+        <v>33.2</v>
       </c>
       <c r="T23" t="n">
-        <v>42.7</v>
+        <v>42.5</v>
       </c>
       <c r="U23" t="n">
         <v>20.6</v>
       </c>
       <c r="V23" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W23" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X23" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Y23" t="n">
         <v>5.9</v>
@@ -4552,67 +4619,67 @@
         <v>20.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC23" t="n">
         <v>-3.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AE23" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AF23" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AG23" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AH23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI23" t="n">
         <v>19</v>
       </c>
       <c r="AJ23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AK23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN23" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AO23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR23" t="n">
         <v>27</v>
       </c>
-      <c r="AP23" t="n">
-        <v>23</v>
-      </c>
-      <c r="AQ23" t="n">
+      <c r="AS23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AU23" t="n">
         <v>20</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>28</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>20</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>19</v>
       </c>
       <c r="AV23" t="n">
         <v>16</v>
@@ -4621,19 +4688,19 @@
         <v>15</v>
       </c>
       <c r="AX23" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AY23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA23" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BB23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC23" t="n">
         <v>22</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-2-2013-14</t>
+          <t>2014-01-02</t>
         </is>
       </c>
     </row>
@@ -4665,94 +4732,94 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F24" t="n">
         <v>21</v>
       </c>
       <c r="G24" t="n">
-        <v>0.344</v>
+        <v>0.323</v>
       </c>
       <c r="H24" t="n">
         <v>49.1</v>
       </c>
       <c r="I24" t="n">
-        <v>39.7</v>
+        <v>39.6</v>
       </c>
       <c r="J24" t="n">
         <v>89.3</v>
       </c>
       <c r="K24" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L24" t="n">
         <v>7.5</v>
       </c>
       <c r="M24" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="O24" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="P24" t="n">
         <v>22.8</v>
       </c>
-      <c r="N24" t="n">
-        <v>0.328</v>
-      </c>
-      <c r="O24" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="P24" t="n">
-        <v>23</v>
-      </c>
       <c r="Q24" t="n">
-        <v>0.716</v>
+        <v>0.714</v>
       </c>
       <c r="R24" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S24" t="n">
         <v>33.4</v>
       </c>
       <c r="T24" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
       <c r="U24" t="n">
         <v>23.1</v>
       </c>
       <c r="V24" t="n">
-        <v>17.5</v>
+        <v>17.7</v>
       </c>
       <c r="W24" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="Y24" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="Z24" t="n">
-        <v>21.5</v>
+        <v>21.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>103.3</v>
+        <v>103</v>
       </c>
       <c r="AC24" t="n">
-        <v>-7.7</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AD24" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AE24" t="n">
         <v>23</v>
       </c>
       <c r="AF24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH24" t="n">
         <v>3</v>
@@ -4764,7 +4831,7 @@
         <v>1</v>
       </c>
       <c r="AK24" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AL24" t="n">
         <v>15</v>
@@ -4776,7 +4843,7 @@
         <v>27</v>
       </c>
       <c r="AO24" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AP24" t="n">
         <v>15</v>
@@ -4785,40 +4852,40 @@
         <v>28</v>
       </c>
       <c r="AR24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT24" t="n">
         <v>5</v>
       </c>
       <c r="AU24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
       </c>
       <c r="AW24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY24" t="n">
         <v>30</v>
       </c>
       <c r="AZ24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA24" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BB24" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BC24" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-2-2013-14</t>
+          <t>2014-01-02</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E25" t="n">
         <v>19</v>
       </c>
       <c r="F25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G25" t="n">
-        <v>0.613</v>
+        <v>0.633</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
@@ -4865,46 +4932,46 @@
         <v>38.3</v>
       </c>
       <c r="J25" t="n">
-        <v>83.3</v>
+        <v>83</v>
       </c>
       <c r="K25" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L25" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="N25" t="n">
-        <v>0.369</v>
+        <v>0.373</v>
       </c>
       <c r="O25" t="n">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
       <c r="P25" t="n">
-        <v>23.2</v>
+        <v>23.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.739</v>
+        <v>0.743</v>
       </c>
       <c r="R25" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="S25" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="T25" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="U25" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="V25" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="W25" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X25" t="n">
         <v>5.4</v>
@@ -4913,19 +4980,19 @@
         <v>4</v>
       </c>
       <c r="Z25" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>103.3</v>
+        <v>103.7</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE25" t="n">
         <v>9</v>
@@ -4934,7 +5001,7 @@
         <v>6</v>
       </c>
       <c r="AG25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AH25" t="n">
         <v>24</v>
@@ -4943,7 +5010,7 @@
         <v>12</v>
       </c>
       <c r="AJ25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AK25" t="n">
         <v>9</v>
@@ -4952,34 +5019,34 @@
         <v>2</v>
       </c>
       <c r="AM25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO25" t="n">
         <v>14</v>
       </c>
       <c r="AP25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT25" t="n">
         <v>14</v>
       </c>
-      <c r="AQ25" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>13</v>
-      </c>
       <c r="AU25" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AV25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW25" t="n">
         <v>7</v>
@@ -4988,19 +5055,19 @@
         <v>8</v>
       </c>
       <c r="AY25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ25" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BC25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-2-2013-14</t>
+          <t>2014-01-02</t>
         </is>
       </c>
     </row>
@@ -5029,94 +5096,94 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F26" t="n">
         <v>7</v>
       </c>
       <c r="G26" t="n">
-        <v>0.788</v>
+        <v>0.781</v>
       </c>
       <c r="H26" t="n">
         <v>48.5</v>
       </c>
       <c r="I26" t="n">
-        <v>40.2</v>
+        <v>39.8</v>
       </c>
       <c r="J26" t="n">
-        <v>87.7</v>
+        <v>87.5</v>
       </c>
       <c r="K26" t="n">
-        <v>0.459</v>
+        <v>0.455</v>
       </c>
       <c r="L26" t="n">
-        <v>10.6</v>
+        <v>10.3</v>
       </c>
       <c r="M26" t="n">
-        <v>26.1</v>
+        <v>25.9</v>
       </c>
       <c r="N26" t="n">
-        <v>0.405</v>
+        <v>0.396</v>
       </c>
       <c r="O26" t="n">
-        <v>18</v>
+        <v>18.4</v>
       </c>
       <c r="P26" t="n">
-        <v>21.9</v>
+        <v>22.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.819</v>
+        <v>0.82</v>
       </c>
       <c r="R26" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="S26" t="n">
-        <v>33.2</v>
+        <v>33</v>
       </c>
       <c r="T26" t="n">
-        <v>46.1</v>
+        <v>45.9</v>
       </c>
       <c r="U26" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="V26" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="W26" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="X26" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.2</v>
+        <v>20.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>109</v>
+        <v>108.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
       </c>
       <c r="AF26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH26" t="n">
         <v>13</v>
@@ -5128,22 +5195,22 @@
         <v>3</v>
       </c>
       <c r="AK26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL26" t="n">
         <v>1</v>
       </c>
       <c r="AM26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN26" t="n">
         <v>2</v>
       </c>
-      <c r="AN26" t="n">
-        <v>1</v>
-      </c>
       <c r="AO26" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AP26" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
@@ -5155,10 +5222,10 @@
         <v>8</v>
       </c>
       <c r="AT26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV26" t="n">
         <v>5</v>
@@ -5167,7 +5234,7 @@
         <v>30</v>
       </c>
       <c r="AX26" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
@@ -5176,7 +5243,7 @@
         <v>3</v>
       </c>
       <c r="BA26" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BB26" t="n">
         <v>1</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-2-2013-14</t>
+          <t>2014-01-02</t>
         </is>
       </c>
     </row>
@@ -5211,106 +5278,106 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E27" t="n">
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G27" t="n">
-        <v>0.323</v>
+        <v>0.333</v>
       </c>
       <c r="H27" t="n">
         <v>48.5</v>
       </c>
       <c r="I27" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="J27" t="n">
         <v>83.3</v>
       </c>
       <c r="K27" t="n">
-        <v>0.444</v>
+        <v>0.445</v>
       </c>
       <c r="L27" t="n">
         <v>6.9</v>
       </c>
       <c r="M27" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="N27" t="n">
-        <v>0.34</v>
+        <v>0.341</v>
       </c>
       <c r="O27" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="P27" t="n">
-        <v>25.4</v>
+        <v>25</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.774</v>
+        <v>0.776</v>
       </c>
       <c r="R27" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="S27" t="n">
-        <v>31.1</v>
+        <v>31</v>
       </c>
       <c r="T27" t="n">
-        <v>42.6</v>
+        <v>42.3</v>
       </c>
       <c r="U27" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="V27" t="n">
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
       <c r="W27" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X27" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="Z27" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>22.4</v>
+        <v>22.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>100.5</v>
+        <v>100.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>-3.7</v>
+        <v>-3.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE27" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AF27" t="n">
         <v>23</v>
       </c>
       <c r="AG27" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AH27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI27" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK27" t="n">
         <v>18</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>14</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>20</v>
       </c>
       <c r="AL27" t="n">
         <v>22</v>
@@ -5319,16 +5386,16 @@
         <v>19</v>
       </c>
       <c r="AN27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO27" t="n">
         <v>7</v>
       </c>
       <c r="AP27" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AQ27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR27" t="n">
         <v>12</v>
@@ -5337,13 +5404,13 @@
         <v>21</v>
       </c>
       <c r="AT27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU27" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AV27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW27" t="n">
         <v>12</v>
@@ -5352,7 +5419,7 @@
         <v>29</v>
       </c>
       <c r="AY27" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AZ27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-2-2013-14</t>
+          <t>2014-01-02</t>
         </is>
       </c>
     </row>
@@ -5393,94 +5460,94 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E28" t="n">
         <v>25</v>
       </c>
       <c r="F28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G28" t="n">
-        <v>0.758</v>
+        <v>0.781</v>
       </c>
       <c r="H28" t="n">
         <v>48</v>
       </c>
       <c r="I28" t="n">
-        <v>40.6</v>
+        <v>40.8</v>
       </c>
       <c r="J28" t="n">
-        <v>83.8</v>
+        <v>84</v>
       </c>
       <c r="K28" t="n">
         <v>0.485</v>
       </c>
       <c r="L28" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>21.1</v>
+        <v>20.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0.399</v>
+        <v>0.397</v>
       </c>
       <c r="O28" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="P28" t="n">
         <v>18.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.767</v>
+        <v>0.769</v>
       </c>
       <c r="R28" t="n">
         <v>9.4</v>
       </c>
       <c r="S28" t="n">
-        <v>33.4</v>
+        <v>33.7</v>
       </c>
       <c r="T28" t="n">
-        <v>42.8</v>
+        <v>43.1</v>
       </c>
       <c r="U28" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="V28" t="n">
         <v>14.5</v>
       </c>
       <c r="W28" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X28" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y28" t="n">
         <v>4.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>104</v>
+        <v>104.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH28" t="n">
         <v>27</v>
@@ -5495,13 +5562,13 @@
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AM28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO28" t="n">
         <v>29</v>
@@ -5510,16 +5577,16 @@
         <v>29</v>
       </c>
       <c r="AQ28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AR28" t="n">
         <v>26</v>
       </c>
       <c r="AS28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AU28" t="n">
         <v>2</v>
@@ -5531,7 +5598,7 @@
         <v>13</v>
       </c>
       <c r="AX28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY28" t="n">
         <v>16</v>
@@ -5540,7 +5607,7 @@
         <v>2</v>
       </c>
       <c r="BA28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB28" t="n">
         <v>7</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-2-2013-14</t>
+          <t>2014-01-02</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>1.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AE29" t="n">
         <v>13</v>
@@ -5671,7 +5738,7 @@
         <v>25</v>
       </c>
       <c r="AJ29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK29" t="n">
         <v>23</v>
@@ -5686,10 +5753,10 @@
         <v>18</v>
       </c>
       <c r="AO29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AQ29" t="n">
         <v>6</v>
@@ -5701,16 +5768,16 @@
         <v>20</v>
       </c>
       <c r="AT29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV29" t="n">
         <v>12</v>
       </c>
       <c r="AW29" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AX29" t="n">
         <v>19</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-2-2013-14</t>
+          <t>2014-01-02</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F30" t="n">
         <v>24</v>
       </c>
       <c r="G30" t="n">
-        <v>0.314</v>
+        <v>0.294</v>
       </c>
       <c r="H30" t="n">
         <v>48.3</v>
@@ -5775,7 +5842,7 @@
         <v>35.4</v>
       </c>
       <c r="J30" t="n">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K30" t="n">
         <v>0.431</v>
@@ -5784,37 +5851,37 @@
         <v>6.4</v>
       </c>
       <c r="M30" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0.349</v>
+        <v>0.347</v>
       </c>
       <c r="O30" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="P30" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.764</v>
+        <v>0.759</v>
       </c>
       <c r="R30" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S30" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="T30" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="U30" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="V30" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W30" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X30" t="n">
         <v>5</v>
@@ -5823,16 +5890,16 @@
         <v>5.3</v>
       </c>
       <c r="Z30" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="AA30" t="n">
         <v>20.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>92.8</v>
+        <v>92.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>-7.7</v>
+        <v>-8.1</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
@@ -5844,7 +5911,7 @@
         <v>29</v>
       </c>
       <c r="AG30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AH30" t="n">
         <v>23</v>
@@ -5856,7 +5923,7 @@
         <v>24</v>
       </c>
       <c r="AK30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL30" t="n">
         <v>26</v>
@@ -5865,34 +5932,34 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AO30" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AP30" t="n">
         <v>25</v>
       </c>
       <c r="AQ30" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AR30" t="n">
         <v>11</v>
       </c>
       <c r="AS30" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AT30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU30" t="n">
         <v>25</v>
       </c>
       <c r="AV30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW30" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AX30" t="n">
         <v>12</v>
@@ -5901,16 +5968,16 @@
         <v>18</v>
       </c>
       <c r="AZ30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-2-2013-14</t>
+          <t>2014-01-02</t>
         </is>
       </c>
     </row>
@@ -6038,7 +6105,7 @@
         <v>10</v>
       </c>
       <c r="AK31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL31" t="n">
         <v>10</v>
@@ -6053,19 +6120,19 @@
         <v>28</v>
       </c>
       <c r="AP31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ31" t="n">
         <v>23</v>
       </c>
       <c r="AR31" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AS31" t="n">
         <v>19</v>
       </c>
       <c r="AT31" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AU31" t="n">
         <v>8</v>
@@ -6077,7 +6144,7 @@
         <v>8</v>
       </c>
       <c r="AX31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY31" t="n">
         <v>5</v>
@@ -6086,7 +6153,7 @@
         <v>10</v>
       </c>
       <c r="BA31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB31" t="n">
         <v>19</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-2-2013-14</t>
+          <t>2014-01-02</t>
         </is>
       </c>
     </row>
